--- a/product_upload/packages/25/file.xlsx
+++ b/product_upload/packages/25/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -838,6 +843,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>SENERGY 5 MG/160 MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-8B867D12E2D4</t>
         </is>
       </c>
@@ -861,7 +871,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1024,6 +1034,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>GLERAN 15MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-F3F6A545BE5A</t>
         </is>
       </c>
@@ -1047,7 +1062,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1210,6 +1225,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>GLERAN 30MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-5D5549ABEBCF</t>
         </is>
       </c>
@@ -1233,7 +1253,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1400,6 +1420,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>OROTIX 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-681ACF8E2598</t>
         </is>
       </c>
@@ -1423,7 +1448,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1590,6 +1615,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>OROTIX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-E841C5617277</t>
         </is>
       </c>
@@ -1613,7 +1643,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1776,6 +1806,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>OROTIX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-391D0627E7F0</t>
         </is>
       </c>
@@ -1799,7 +1834,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1954,6 +1989,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>LUKRA 5MG CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-280B3A625740</t>
         </is>
       </c>
@@ -1977,7 +2017,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2136,6 +2176,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>LUKRA 4MG CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-1A0AB6FFDF55</t>
         </is>
       </c>
@@ -2159,7 +2204,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2326,6 +2371,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>TERA D 50000IU CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-B6613D1F0C5C</t>
         </is>
       </c>
@@ -2349,7 +2399,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2516,6 +2566,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>OMEGANA 1000MG SOFT CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-8AE8E62D70E7</t>
         </is>
       </c>
@@ -2539,7 +2594,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2706,6 +2761,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>OMEGANA 1000MG SOFT CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-CFC3134527F3</t>
         </is>
       </c>
@@ -2729,7 +2789,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2892,6 +2952,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t xml:space="preserve">REDEX 5 MG F.C.TABLET  </t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-04BAB990C390</t>
         </is>
       </c>
@@ -2915,7 +2980,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3086,6 +3151,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t xml:space="preserve">REDEX 20MG F.C.TABLET                                     </t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-1749B396867F</t>
         </is>
       </c>
@@ -3109,7 +3179,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3276,6 +3346,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>ROZLET 2.5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-D2B5728DD77B</t>
         </is>
       </c>
@@ -3299,7 +3374,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3466,6 +3541,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>ABIRATERONE SPC 250MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-B45C37553E84</t>
         </is>
       </c>
@@ -3489,7 +3569,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3652,6 +3732,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>OXYNORM 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-179D8D46B5C5</t>
         </is>
       </c>
@@ -3675,7 +3760,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3834,6 +3919,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>OXYNORM 10MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-6D9B45A3BFB0</t>
         </is>
       </c>
@@ -3857,7 +3947,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4016,6 +4106,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>OXYNORM 20MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-F9B76D1BA7AE</t>
         </is>
       </c>
@@ -4039,7 +4134,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4194,6 +4289,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>LUKRA 10 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-CBF63E1A7DCC</t>
         </is>
       </c>
@@ -4217,7 +4317,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4380,6 +4480,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>Juvamox</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-E673E14B3E5A</t>
         </is>
       </c>
@@ -4403,7 +4508,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4566,6 +4671,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>Juvamox 500MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-95C9C2D9F1CE</t>
         </is>
       </c>
@@ -4589,7 +4699,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4752,6 +4862,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>JUSPRIN 81MG ENTERIC COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-1022CD9B808E</t>
         </is>
       </c>
@@ -4775,7 +4890,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4934,6 +5049,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>KAPTIN SUSP</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-1096D8177D45</t>
         </is>
       </c>
@@ -4957,7 +5077,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5116,6 +5236,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>KDIRON DROPS</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-AEEF0C04FCA7</t>
         </is>
       </c>
@@ -5139,7 +5264,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5310,6 +5435,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>LANFAST 30MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-AEBF26CA857D</t>
         </is>
       </c>
@@ -5333,7 +5463,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5496,6 +5626,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>LAXOCODYL 10MG SUPP</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-BC39271B3FA2</t>
         </is>
       </c>
@@ -5519,7 +5654,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5682,6 +5817,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>LAXOCODYL 5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-A5EA60EEC0D4</t>
         </is>
       </c>
@@ -5705,7 +5845,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5876,6 +6016,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>LAXOCODYL 5MG SUPP</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-18E18C633E6B</t>
         </is>
       </c>
@@ -5899,7 +6044,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6066,6 +6211,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>LAXOLYNE SUPP FOR CHILDREN</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-8F165C033FD5</t>
         </is>
       </c>
@@ -6089,7 +6239,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6248,6 +6398,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>LAXOLYNE SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-8BD116539C74</t>
         </is>
       </c>
@@ -6271,7 +6426,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6430,6 +6585,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>JULMENTIN FORTE 312.5MG POWDER FOR SUSP</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-3642440C80D1</t>
         </is>
       </c>
@@ -6453,7 +6613,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6612,6 +6772,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>JULMENTIN 625 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-4B6D4207E31B</t>
         </is>
       </c>
@@ -6635,7 +6800,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6794,6 +6959,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>GLYPRIDE 3 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-F7F2BA5862AA</t>
         </is>
       </c>
@@ -6817,7 +6987,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6984,6 +7154,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>GUPISONE TAB 5MG</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-18E27030848B</t>
         </is>
       </c>
@@ -7007,7 +7182,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7166,6 +7341,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>GYNO-MIKOZAL 200MG VAG.OVULE</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-CE6853783121</t>
         </is>
       </c>
@@ -7189,7 +7369,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7360,6 +7540,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>GYNO-MIKOZAL 400MG VAG.OVULE</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-EB787CDC8C9B</t>
         </is>
       </c>
@@ -7383,7 +7568,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7550,6 +7735,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>GYNO-MIKOZAL CREAM 78 GM</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-1254DB03C041</t>
         </is>
       </c>
@@ -7573,7 +7763,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7740,6 +7930,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t xml:space="preserve">HAEMOPROCT </t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-79900BCCF754</t>
         </is>
       </c>
@@ -7763,7 +7958,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7922,6 +8117,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>HISTALOC 25MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-AACF241A8F77</t>
         </is>
       </c>
@@ -7945,7 +8145,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8112,6 +8312,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>HISTALOC 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-6B782674042A</t>
         </is>
       </c>
@@ -8135,7 +8340,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8298,6 +8503,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>JULMENTIN 156.25 MG POWDER FOR SUSP</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-0C793E86A0D5</t>
         </is>
       </c>
@@ -8321,7 +8531,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8476,6 +8686,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>JULMENTIN 2X. 1000MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-98F4B77E9CE2</t>
         </is>
       </c>
@@ -8499,7 +8714,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8658,6 +8873,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>JULMENTIN 2X. 457MG-5ML ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-7E6B9A46BA6D</t>
         </is>
       </c>
@@ -8681,7 +8901,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8840,6 +9060,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>JULMENTIN 375 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-301D29136717</t>
         </is>
       </c>
@@ -8863,7 +9088,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9018,6 +9243,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>IBUGESIC</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-CC4779902A8D</t>
         </is>
       </c>
@@ -9041,7 +9271,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9208,6 +9438,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>LIDOCAINE 5 % OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-9201D571F16B</t>
         </is>
       </c>
@@ -9231,7 +9466,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9402,6 +9637,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>MIKOSTAT 100000 U OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-37E59BD2F2F0</t>
         </is>
       </c>
@@ -9425,7 +9665,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9584,6 +9824,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>MIKOSTAT 100000U CREAM</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-5428A33417A6</t>
         </is>
       </c>
@@ -9607,7 +9852,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9774,6 +10019,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>MIKOSTAT 100000U\ML ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-79415297CE2C</t>
         </is>
       </c>
@@ -9797,7 +10047,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9956,6 +10206,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>MIKOZAL 2% cream</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-AC5CE862E7E8</t>
         </is>
       </c>
@@ -9979,7 +10234,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10138,6 +10393,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>MIXAVIT SYRUP</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-2BB5DC67EC68</t>
         </is>
       </c>
@@ -10161,7 +10421,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10318,6 +10578,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>MIXAVIT TAB</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-DFCE0C843A24</t>
         </is>
       </c>
@@ -10341,7 +10606,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10500,6 +10765,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>MODODOM 10MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-1D1306A4F687</t>
         </is>
       </c>
@@ -10523,7 +10793,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10678,6 +10948,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>MODODOM 1MG-1ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-61C13C5A334E</t>
         </is>
       </c>
@@ -10701,7 +10976,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10868,6 +11143,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>MOXAL PLUS Suspension</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-383231F47EBE</t>
         </is>
       </c>
@@ -10891,7 +11171,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11058,6 +11338,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>MOXAL PLUS Tablet</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-A897C1FCB4CE</t>
         </is>
       </c>
@@ -11081,7 +11366,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11252,6 +11537,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>MOXAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-C7A64274EDAC</t>
         </is>
       </c>
@@ -11275,7 +11565,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11450,6 +11740,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>MOXAL Tablet</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-5BFF81933FC2</t>
         </is>
       </c>
@@ -11473,7 +11768,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11634,6 +11929,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>MIXAVIT DROPS 15ML</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-603AD75C31EA</t>
         </is>
       </c>
@@ -11657,7 +11957,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11820,6 +12120,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>GLYPRIDE 2 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-A9768B40770A</t>
         </is>
       </c>
@@ -11843,7 +12148,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12006,6 +12311,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>LOJOUR 5MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-F658130AC405</t>
         </is>
       </c>
@@ -12029,7 +12339,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12192,6 +12502,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>LOMAX 400MG TAB</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-0493893C1D2A</t>
         </is>
       </c>
@@ -12215,7 +12530,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12370,6 +12685,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>LOMAX 400MG TAB</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-144BC3FADEFE</t>
         </is>
       </c>
@@ -12393,7 +12713,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12556,6 +12876,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>LORADAY 10MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-930169BA4599</t>
         </is>
       </c>
@@ -12579,7 +12904,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12746,6 +13071,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>Purout 300 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-274DDDCD0E63</t>
         </is>
       </c>
@@ -12769,7 +13099,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12924,6 +13254,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>LOVRAK 5% cream</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-1AF2C90E1964</t>
         </is>
       </c>
@@ -12947,7 +13282,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13102,6 +13437,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>LOVRAK 5% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-B426DE5AC8F1</t>
         </is>
       </c>
@@ -13125,7 +13465,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13284,6 +13624,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>LOVRAK 800 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-053D95690B61</t>
         </is>
       </c>
@@ -13307,7 +13652,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13470,6 +13815,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>LORADAD 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-160FE48CA1A9</t>
         </is>
       </c>
@@ -13493,7 +13843,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13648,6 +13998,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>GLYPRIDE 1 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-2D6C555B5E2F</t>
         </is>
       </c>
@@ -13671,7 +14026,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13830,6 +14185,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>DEXIPAN 5%  CREAM</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-D671CE1EA432</t>
         </is>
       </c>
@@ -13853,7 +14213,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14012,6 +14372,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>DIALON 1000MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-03FDA4A6B6AE</t>
         </is>
       </c>
@@ -14035,7 +14400,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14194,6 +14559,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>DIALON 500 MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-093AD75BFB0A</t>
         </is>
       </c>
@@ -14217,7 +14587,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14376,6 +14746,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>DIALON 850MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-076B8E35D22A</t>
         </is>
       </c>
@@ -14399,7 +14774,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14570,6 +14945,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>DICLOGESIC RETARD</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-78E8CB71D63E</t>
         </is>
       </c>
@@ -14593,7 +14973,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14760,6 +15140,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>DIZINIL 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-5B3853E3AB54</t>
         </is>
       </c>
@@ -14783,7 +15168,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14954,6 +15339,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>DOXYDAR</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-C3B5A7C1AC55</t>
         </is>
       </c>
@@ -14977,7 +15367,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15140,6 +15530,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>DURADOX 100 MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-6DCA15083BFB</t>
         </is>
       </c>
@@ -15163,7 +15558,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15326,6 +15721,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>DICLOGESIC RETARD</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-0BFFA2084512</t>
         </is>
       </c>
@@ -15349,7 +15749,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15512,6 +15912,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>CIPRODAR 500</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-F8C857EC8E85</t>
         </is>
       </c>
@@ -15535,7 +15940,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15698,6 +16103,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>CLAMYCIN 500 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-DF65671F1592</t>
         </is>
       </c>
@@ -15721,7 +16131,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15888,6 +16298,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>CLARIDAR</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-7BD52EA4126B</t>
         </is>
       </c>
@@ -15911,7 +16326,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16074,6 +16489,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>CLARIDAR 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-640DF8FEE713</t>
         </is>
       </c>
@@ -16097,7 +16517,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16260,6 +16680,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>CLOFEN CREAMAGEL 1%</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-315C4EB4F171</t>
         </is>
       </c>
@@ -16283,7 +16708,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16446,6 +16871,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>CLOFEN CREAMAGEL 1%</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-4367B319967E</t>
         </is>
       </c>
@@ -16469,7 +16899,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16628,6 +17058,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>CLAREX 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-CD3A5BAB08B0</t>
         </is>
       </c>
@@ -16651,7 +17086,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16814,6 +17249,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>MUCOLYTE SYRUP</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-41497D9AB15F</t>
         </is>
       </c>
@@ -16837,7 +17277,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17004,6 +17444,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>FOLICUM 1 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-1CB6C9CE5CFB</t>
         </is>
       </c>
@@ -17027,7 +17472,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17186,6 +17631,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>FOLICUM 5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-2DB8EEEFBD6D</t>
         </is>
       </c>
@@ -17209,7 +17659,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17380,6 +17830,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>FUSIX 40MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-98F2C0C690A0</t>
         </is>
       </c>
@@ -17403,7 +17858,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17562,6 +18017,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>FUTASOLE 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-6B73944E2F30</t>
         </is>
       </c>
@@ -17585,7 +18045,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17744,6 +18204,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>FUTASOLE 2%CREAM</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-78CCD99ED002</t>
         </is>
       </c>
@@ -17767,7 +18232,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17930,6 +18395,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>GAMAVATE 0.05% ointment</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-0D4E3718DC5C</t>
         </is>
       </c>
@@ -17953,7 +18423,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18116,6 +18586,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>GAMAVATE 0.05% cream</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-5134C941A87C</t>
         </is>
       </c>
@@ -18139,7 +18614,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18302,6 +18777,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>EROMYCIN 200MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-49B557A3C956</t>
         </is>
       </c>
@@ -18325,7 +18805,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18496,6 +18976,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>ERYTHRODAR</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-3DC71BB3E7AA</t>
         </is>
       </c>
@@ -18519,7 +19004,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18686,6 +19171,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>ERYTHRODAR 400MG FORT TAB</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-43AEC5CFFE32</t>
         </is>
       </c>
@@ -18709,7 +19199,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18868,6 +19358,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>FLOXACIN 500 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-686C3BA6A565</t>
         </is>
       </c>
@@ -18891,7 +19386,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19058,6 +19553,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>FAMODAR</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-6AE48C899990</t>
         </is>
       </c>
@@ -19081,7 +19581,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19243,6 +19743,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>FAMODAR</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-00186F7A7230</t>
         </is>
@@ -19259,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19305,100 +19810,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19430,7 +19940,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19445,92 +19955,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-94937</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>404.7</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>175</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19562,7 +20077,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19577,92 +20092,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-37828</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>286.2</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>176</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19694,7 +20214,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19709,92 +20229,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-74840</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>272.96</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>177</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19826,7 +20351,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19841,92 +20366,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-31816</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>150.05</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>178</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19958,7 +20488,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19973,92 +20503,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-61398</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>342.46</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>179</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20090,7 +20625,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20105,92 +20640,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-68029</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>197.64</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>180</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20222,7 +20762,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20237,92 +20777,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-78276</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>435.36</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>181</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20354,7 +20899,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20369,92 +20914,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-59846</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>172.23</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>182</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20486,7 +21036,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20501,92 +21051,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-36815</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>112.08</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>183</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20618,7 +21173,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20633,92 +21188,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-80765</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>265.11</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>184</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20750,7 +21310,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20765,92 +21325,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-66392</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>455.59</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>185</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20867,7 +21432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20973,6 +21538,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21008,7 +21583,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21073,6 +21648,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-971DE68D7086</t>
         </is>
@@ -21109,7 +21694,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21174,6 +21759,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-80F0E5B223E6</t>
         </is>
@@ -21210,7 +21805,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21275,6 +21870,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-FE4B1E063C6C</t>
         </is>
@@ -21311,7 +21916,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21376,6 +21981,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-35FE4DFC2AFB</t>
         </is>
@@ -21412,7 +22027,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21477,6 +22092,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-8068DD430B81</t>
         </is>
@@ -21513,7 +22138,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21578,6 +22203,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-34FAD35B274D</t>
         </is>
@@ -21614,7 +22249,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21679,6 +22314,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-92257DB471C9</t>
         </is>
@@ -21715,7 +22360,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21780,6 +22425,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-E41788C2EA72</t>
         </is>
@@ -21816,7 +22471,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21881,6 +22536,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-CD5A3225F5CC</t>
         </is>
@@ -21917,7 +22582,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21982,6 +22647,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-7E466097B864</t>
         </is>
@@ -22018,7 +22693,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22083,6 +22758,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-1230BA319669</t>
         </is>
@@ -22119,7 +22804,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22184,6 +22869,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-AAAD36176FAF</t>
         </is>
@@ -22220,7 +22915,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22285,6 +22980,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-5C261C85F4AF</t>
         </is>
@@ -22321,7 +23026,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22386,6 +23091,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-0070AFA2A24C</t>
         </is>
@@ -22422,7 +23137,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22487,6 +23202,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-8F637F78846F</t>
         </is>
@@ -22523,7 +23248,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22588,6 +23313,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-8290FE3B71DD</t>
         </is>
@@ -22624,7 +23359,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22689,6 +23424,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-A94A3C17A324</t>
         </is>
@@ -22725,7 +23470,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22790,6 +23535,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-E4D4196D0911</t>
         </is>
@@ -22826,7 +23581,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22891,6 +23646,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-D9487E6927A0</t>
         </is>
@@ -22927,7 +23692,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22992,6 +23757,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-D222080E340D</t>
         </is>

--- a/product_upload/packages/25/file.xlsx
+++ b/product_upload/packages/25/file.xlsx
@@ -879,8 +879,16 @@
           <t>8683311999-340-904314588298</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLERAN 15MG TABLET</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>GLERAN 15MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1070,8 +1078,16 @@
           <t>0039901126-464-575840979757</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLERAN 30MG TABLET</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>GLERAN 30MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1261,8 +1277,16 @@
           <t>7216092027-287-497018458101</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OROTIX 60MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OROTIX 60MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1456,8 +1480,16 @@
           <t>5338033236-374-299758750832</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OROTIX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OROTIX 90MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1651,8 +1683,16 @@
           <t>6179829704-525-702090280309</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OROTIX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>OROTIX 120MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1842,8 +1882,16 @@
           <t>1450488730-141-801441454399</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LUKRA 5MG CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LUKRA 5MG CHEWABLE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2025,8 +2073,16 @@
           <t>1917484352-869-202670240187</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LUKRA 4MG CHEWABLE TABLET</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LUKRA 4MG CHEWABLE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2212,8 +2268,16 @@
           <t>1401297763-966-181695620962</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TERA D 50000IU CAPSULE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TERA D 50000IU CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2797,8 +2861,16 @@
           <t>8449978824-790-197661654016</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REDEX 5 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>REDEX 5 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3577,8 +3649,16 @@
           <t>5501651094-872-058144194091</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OXYNORM 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>OXYNORM 5MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3768,8 +3848,16 @@
           <t>2896730539-103-154610078049</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OXYNORM 10MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>OXYNORM 10MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3955,8 +4043,16 @@
           <t>4120587738-714-694456060543</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OXYNORM 20MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>OXYNORM 20MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4142,8 +4238,16 @@
           <t>9210393132-662-854069179575</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LUKRA 10 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>LUKRA 10 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4325,8 +4429,16 @@
           <t>8425807779-227-867172168556</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Juvamox</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Juvamox detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4516,8 +4628,16 @@
           <t>0381334257-611-859913582952</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Juvamox 500MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Juvamox 500MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4707,8 +4827,16 @@
           <t>9384371432-445-799957731807</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JUSPRIN 81MG ENTERIC COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>JUSPRIN 81MG ENTERIC COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4898,8 +5026,16 @@
           <t>8925717769-620-950359489847</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KAPTIN SUSP</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>KAPTIN SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5085,8 +5221,16 @@
           <t>1705967188-657-702130671437</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KDIRON DROPS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>KDIRON DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5662,8 +5806,16 @@
           <t>1125249321-766-278934531545</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAXOCODYL 5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>LAXOCODYL 5 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -6247,8 +6399,16 @@
           <t>8946631952-469-952343261136</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAXOLYNE SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>LAXOLYNE SUPPOSITORIES detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6434,8 +6594,16 @@
           <t>5727660278-954-135868475752</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN FORTE 312.5MG POWDER FOR SUSP</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>JULMENTIN FORTE 312.5MG POWDER FOR SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6621,8 +6789,16 @@
           <t>6820411042-640-155752003385</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN 625 MG TAB</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>JULMENTIN 625 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6808,8 +6984,16 @@
           <t>3799582779-798-074029806030</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYPRIDE 3 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>GLYPRIDE 3 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7190,8 +7374,16 @@
           <t>8671686313-972-260910888047</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GYNO-MIKOZAL 200MG VAG.OVULE</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>GYNO-MIKOZAL 200MG VAG.OVULE detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7966,8 +8158,16 @@
           <t>1560602250-757-069078889232</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HISTALOC 25MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>HISTALOC 25MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8348,8 +8548,16 @@
           <t>6442604880-641-729469107424</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN 156.25 MG POWDER FOR SUSP</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>JULMENTIN 156.25 MG POWDER FOR SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8539,8 +8747,16 @@
           <t>0357664950-638-021468008550</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN 2X. 1000MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>JULMENTIN 2X. 1000MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8722,8 +8938,16 @@
           <t>6714782025-196-255827298542</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN 2X. 457MG-5ML ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>JULMENTIN 2X. 457MG-5ML ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8909,8 +9133,16 @@
           <t>1172423410-687-562692104480</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN 375 MG TAB</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>JULMENTIN 375 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9096,8 +9328,16 @@
           <t>4558320411-636-156567146382</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IBUGESIC</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>IBUGESIC detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9279,8 +9519,16 @@
           <t>0478581857-001-983563870255</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIDOCAINE 5 % OINTMENT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>LIDOCAINE 5 % OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9673,8 +9921,16 @@
           <t>3212332422-363-061443940220</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIKOSTAT 100000U CREAM</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>MIKOSTAT 100000U CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -10055,8 +10311,16 @@
           <t>0454937265-939-521367906953</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIKOZAL 2% cream</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>MIKOZAL 2% cream detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10242,8 +10506,16 @@
           <t>3571239592-081-418561309242</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIXAVIT SYRUP</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>MIXAVIT SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10429,8 +10701,16 @@
           <t>2172239948-535-255748630720</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIXAVIT TAB</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>MIXAVIT TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10614,8 +10894,16 @@
           <t>4252011217-307-012991904164</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MODODOM 10MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>MODODOM 10MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10801,8 +11089,16 @@
           <t>9360831097-274-924211433839</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MODODOM 1MG-1ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>MODODOM 1MG-1ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10984,8 +11280,16 @@
           <t>7917686262-932-368488967810</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOXAL PLUS Suspension</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>MOXAL PLUS Suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11179,8 +11483,16 @@
           <t>8001944392-109-454117144401</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOXAL PLUS Tablet</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>MOXAL PLUS Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11776,8 +12088,16 @@
           <t>5770388858-597-675908920119</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIXAVIT DROPS 15ML</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>MIXAVIT DROPS 15ML detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11965,8 +12285,16 @@
           <t>7726584134-244-639076004515</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYPRIDE 2 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>GLYPRIDE 2 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12156,8 +12484,16 @@
           <t>9532096809-003-731083209923</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOJOUR 5MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>LOJOUR 5MG\5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12347,8 +12683,16 @@
           <t>9154083407-112-531226162297</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOMAX 400MG TAB</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>LOMAX 400MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12538,8 +12882,16 @@
           <t>0225366835-882-170541795556</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOMAX 400MG TAB</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>LOMAX 400MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12721,8 +13073,16 @@
           <t>7941682057-455-791805197436</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORADAY 10MG TABLET</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>LORADAY 10MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13107,8 +13467,16 @@
           <t>2434507101-774-758851720848</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOVRAK 5% cream</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>LOVRAK 5% cream detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13290,8 +13658,16 @@
           <t>4821684620-448-750532214598</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOVRAK 5% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>LOVRAK 5% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13473,8 +13849,16 @@
           <t>7992038975-793-761434594143</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOVRAK 800 mg tablet</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>LOVRAK 800 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13660,8 +14044,16 @@
           <t>4909248615-473-629036841856</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORADAD 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>LORADAD 10MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13851,8 +14243,16 @@
           <t>2879643644-500-325704138137</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYPRIDE 1 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>GLYPRIDE 1 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14034,8 +14434,16 @@
           <t>8212575458-831-201694968743</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXIPAN 5%  CREAM</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>DEXIPAN 5%  CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14221,8 +14629,16 @@
           <t>8867958497-968-882923590087</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIALON 1000MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>DIALON 1000MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14408,8 +14824,16 @@
           <t>5643365295-690-073366058572</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIALON 500 MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>DIALON 500 MG F.C TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14595,8 +15019,16 @@
           <t>1020617616-239-692795813516</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIALON 850MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>DIALON 850MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15566,8 +15998,16 @@
           <t>4251593050-113-970254941369</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DICLOGESIC RETARD</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>DICLOGESIC RETARD detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15948,8 +16388,16 @@
           <t>9697134003-623-353828831478</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLAMYCIN 500 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>CLAMYCIN 500 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16334,8 +16782,16 @@
           <t>5927429264-807-748564344421</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARIDAR 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>CLARIDAR 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16525,8 +16981,16 @@
           <t>2771185767-338-051582557211</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOFEN CREAMAGEL 1%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>CLOFEN CREAMAGEL 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16716,8 +17180,16 @@
           <t>8307999609-904-401521291689</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOFEN CREAMAGEL 1%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>CLOFEN CREAMAGEL 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16907,8 +17379,16 @@
           <t>2739262028-775-437713050955</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLAREX 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>CLAREX 500MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17094,8 +17574,16 @@
           <t>5796074587-649-126366177123</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MUCOLYTE SYRUP</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>MUCOLYTE SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17480,8 +17968,16 @@
           <t>6367139589-873-996619770866</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FOLICUM 5MG TAB</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>FOLICUM 5MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17866,8 +18362,16 @@
           <t>7815878902-501-787066152257</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUTASOLE 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>FUTASOLE 2% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18053,8 +18557,16 @@
           <t>7642539338-781-426268900562</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUTASOLE 2%CREAM</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>FUTASOLE 2%CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18240,8 +18752,16 @@
           <t>7005727901-807-205904593419</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GAMAVATE 0.05% ointment</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>GAMAVATE 0.05% ointment detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18431,8 +18951,16 @@
           <t>7191507245-718-386809419347</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GAMAVATE 0.05% cream</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>GAMAVATE 0.05% cream detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18622,8 +19150,16 @@
           <t>1454857595-960-388827129926</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EROMYCIN 200MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>EROMYCIN 200MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19207,8 +19743,16 @@
           <t>0577562820-129-696524992202</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOXACIN 500 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>FLOXACIN 500 MG COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19589,8 +20133,16 @@
           <t>3721734492-299-430068334598</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FAMODAR</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>FAMODAR detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/25/file.xlsx
+++ b/product_upload/packages/25/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20362,7 +20362,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21984,7 +21984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22065,40 +22065,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22178,38 +22183,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>66.2</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-971DE68D7086</t>
         </is>
@@ -22289,38 +22299,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>413</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-80F0E5B223E6</t>
         </is>
@@ -22400,38 +22415,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>370.75</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-FE4B1E063C6C</t>
         </is>
@@ -22511,38 +22531,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>134.96</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-35FE4DFC2AFB</t>
         </is>
@@ -22622,38 +22647,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>285.51</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-8068DD430B81</t>
         </is>
@@ -22733,38 +22763,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>334.54</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-34FAD35B274D</t>
         </is>
@@ -22844,38 +22879,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>271.76</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-92257DB471C9</t>
         </is>
@@ -22955,38 +22995,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>450.21</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-E41788C2EA72</t>
         </is>
@@ -23066,38 +23111,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>255.27</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-CD5A3225F5CC</t>
         </is>
@@ -23177,38 +23227,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>190.93</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-7E466097B864</t>
         </is>
@@ -23288,38 +23343,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-1230BA319669</t>
         </is>
@@ -23399,38 +23459,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>28.67</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-AAAD36176FAF</t>
         </is>
@@ -23510,38 +23575,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>264.41</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-5C261C85F4AF</t>
         </is>
@@ -23621,38 +23691,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>269.18</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-0070AFA2A24C</t>
         </is>
@@ -23732,38 +23807,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>261.42</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-8F637F78846F</t>
         </is>
@@ -23843,38 +23923,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>305.74</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-8290FE3B71DD</t>
         </is>
@@ -23954,38 +24039,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>382.11</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-A94A3C17A324</t>
         </is>
@@ -24065,38 +24155,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>324.23</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-E4D4196D0911</t>
         </is>
@@ -24176,38 +24271,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>31.82</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-D9487E6927A0</t>
         </is>
@@ -24287,38 +24387,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>255.42</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-D222080E340D</t>
         </is>
